--- a/ig/DM-JUILLET-2026/ValueSet-JDV-J107-EnsembleSavoirFaire-RASS.xlsx
+++ b/ig/DM-JUILLET-2026/ValueSet-JDV-J107-EnsembleSavoirFaire-RASS.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="627" uniqueCount="575">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="581">
   <si>
     <t>Property</t>
   </si>
@@ -46,7 +46,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20251222120000</t>
+    <t>20260730120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -73,7 +73,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-12-22T12:00:00+01:00</t>
+    <t>2026-07-30T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -137,6 +137,24 @@
   </si>
   <si>
     <t>Exercice infirmier en pratique avancée urgences (SI)</t>
+  </si>
+  <si>
+    <t>SI06</t>
+  </si>
+  <si>
+    <t>Infirmier(ère) de bloc opératoire (SI)</t>
+  </si>
+  <si>
+    <t>SI07</t>
+  </si>
+  <si>
+    <t>Infirmier(ère) anesthésiste (SI)</t>
+  </si>
+  <si>
+    <t>SI08</t>
+  </si>
+  <si>
+    <t>Exercice infirmier en pratique avancée puériculture (SI)</t>
   </si>
   <si>
     <t>SCD01</t>
@@ -2026,34 +2044,34 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>512</v>
+        <v>518</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>513</v>
+        <v>519</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>514</v>
+        <v>520</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>515</v>
+        <v>521</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>234</v>
+        <v>240</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>516</v>
+        <v>522</v>
       </c>
     </row>
   </sheetData>
@@ -2080,234 +2098,234 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>518</v>
+        <v>524</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>519</v>
+        <v>525</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>520</v>
+        <v>526</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>522</v>
+        <v>528</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>524</v>
+        <v>530</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>525</v>
+        <v>531</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>526</v>
+        <v>532</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>528</v>
+        <v>534</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>529</v>
+        <v>535</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>530</v>
+        <v>536</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>532</v>
+        <v>538</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>534</v>
+        <v>540</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>535</v>
+        <v>541</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>536</v>
+        <v>542</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>537</v>
+        <v>543</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>538</v>
+        <v>544</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>540</v>
+        <v>546</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>542</v>
+        <v>548</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>543</v>
+        <v>549</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>544</v>
+        <v>550</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>546</v>
+        <v>552</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>547</v>
+        <v>553</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>548</v>
+        <v>554</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>549</v>
+        <v>555</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>550</v>
+        <v>556</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>551</v>
+        <v>557</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>552</v>
+        <v>558</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>553</v>
+        <v>559</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>554</v>
+        <v>560</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>555</v>
+        <v>561</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>556</v>
+        <v>562</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>557</v>
+        <v>563</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>558</v>
+        <v>564</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>559</v>
+        <v>565</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>560</v>
+        <v>566</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>561</v>
+        <v>567</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>562</v>
+        <v>568</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>563</v>
+        <v>569</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>564</v>
+        <v>570</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>565</v>
+        <v>571</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>566</v>
+        <v>572</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>567</v>
+        <v>573</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>568</v>
+        <v>574</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>569</v>
+        <v>575</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>570</v>
+        <v>576</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>234</v>
+        <v>240</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>571</v>
+        <v>577</v>
       </c>
     </row>
   </sheetData>
@@ -2334,26 +2352,26 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>572</v>
+        <v>578</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>573</v>
+        <v>579</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>234</v>
+        <v>240</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>574</v>
+        <v>580</v>
       </c>
     </row>
   </sheetData>
@@ -2363,7 +2381,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B106"/>
+  <dimension ref="A1:B109"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -3207,15 +3225,39 @@
         <v>234</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="s" s="2">
+        <v>238</v>
+      </c>
+      <c r="B107" t="s" s="2">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="B108" t="s" s="2">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="s" s="2">
+        <v>241</v>
+      </c>
+      <c r="B109" t="s" s="2">
+        <v>242</v>
       </c>
     </row>
   </sheetData>
@@ -3242,362 +3284,362 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>238</v>
+        <v>244</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>240</v>
+        <v>246</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>242</v>
+        <v>248</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>244</v>
+        <v>250</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>246</v>
+        <v>252</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>248</v>
+        <v>254</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>250</v>
+        <v>256</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>252</v>
+        <v>258</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>254</v>
+        <v>260</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>256</v>
+        <v>262</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>258</v>
+        <v>264</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>260</v>
+        <v>266</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>262</v>
+        <v>268</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>264</v>
+        <v>270</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>266</v>
+        <v>272</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>268</v>
+        <v>274</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>270</v>
+        <v>276</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>272</v>
+        <v>278</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>274</v>
+        <v>280</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>276</v>
+        <v>282</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>278</v>
+        <v>284</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>280</v>
+        <v>286</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>282</v>
+        <v>288</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>284</v>
+        <v>290</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>286</v>
+        <v>292</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>288</v>
+        <v>294</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>290</v>
+        <v>296</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>292</v>
+        <v>298</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>294</v>
+        <v>300</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>296</v>
+        <v>302</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>298</v>
+        <v>304</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>300</v>
+        <v>306</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>302</v>
+        <v>308</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>304</v>
+        <v>310</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>308</v>
+        <v>314</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>310</v>
+        <v>316</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>314</v>
+        <v>320</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>316</v>
+        <v>322</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>318</v>
+        <v>324</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>320</v>
+        <v>326</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>322</v>
+        <v>328</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>234</v>
+        <v>240</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>323</v>
+        <v>329</v>
       </c>
     </row>
   </sheetData>
@@ -3624,50 +3666,50 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>325</v>
+        <v>331</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>327</v>
+        <v>333</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>329</v>
+        <v>335</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>331</v>
+        <v>337</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>234</v>
+        <v>240</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>332</v>
+        <v>338</v>
       </c>
     </row>
   </sheetData>
@@ -3694,346 +3736,346 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>334</v>
+        <v>340</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>336</v>
+        <v>342</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>338</v>
+        <v>344</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>340</v>
+        <v>346</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>342</v>
+        <v>348</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>344</v>
+        <v>350</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>346</v>
+        <v>352</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>348</v>
+        <v>354</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>350</v>
+        <v>356</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>352</v>
+        <v>358</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>354</v>
+        <v>360</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>356</v>
+        <v>362</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>358</v>
+        <v>364</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>360</v>
+        <v>366</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>362</v>
+        <v>368</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>364</v>
+        <v>370</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>366</v>
+        <v>372</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>368</v>
+        <v>374</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>370</v>
+        <v>376</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>372</v>
+        <v>378</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>374</v>
+        <v>380</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>376</v>
+        <v>382</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>378</v>
+        <v>384</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>380</v>
+        <v>386</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>382</v>
+        <v>388</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>384</v>
+        <v>390</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>386</v>
+        <v>392</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>388</v>
+        <v>394</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>390</v>
+        <v>396</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>392</v>
+        <v>398</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>394</v>
+        <v>400</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>396</v>
+        <v>402</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>398</v>
+        <v>404</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>400</v>
+        <v>406</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>402</v>
+        <v>408</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>404</v>
+        <v>410</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>406</v>
+        <v>412</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>408</v>
+        <v>414</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>410</v>
+        <v>416</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>412</v>
+        <v>418</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>414</v>
+        <v>420</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>234</v>
+        <v>240</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>415</v>
+        <v>421</v>
       </c>
     </row>
   </sheetData>
@@ -4060,146 +4102,146 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>417</v>
+        <v>423</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>419</v>
+        <v>425</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>421</v>
+        <v>427</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>423</v>
+        <v>429</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>425</v>
+        <v>431</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>427</v>
+        <v>433</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>428</v>
+        <v>434</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>429</v>
+        <v>435</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>431</v>
+        <v>437</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>433</v>
+        <v>439</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>435</v>
+        <v>441</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>437</v>
+        <v>443</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>439</v>
+        <v>445</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>441</v>
+        <v>447</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>443</v>
+        <v>449</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>445</v>
+        <v>451</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>447</v>
+        <v>453</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>234</v>
+        <v>240</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>448</v>
+        <v>454</v>
       </c>
     </row>
   </sheetData>
@@ -4226,26 +4268,26 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>450</v>
+        <v>456</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>234</v>
+        <v>240</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>451</v>
+        <v>457</v>
       </c>
     </row>
   </sheetData>
@@ -4272,58 +4314,58 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>453</v>
+        <v>459</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>455</v>
+        <v>461</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>457</v>
+        <v>463</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>459</v>
+        <v>465</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>460</v>
+        <v>466</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>461</v>
+        <v>467</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>234</v>
+        <v>240</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>462</v>
+        <v>468</v>
       </c>
     </row>
   </sheetData>
@@ -4350,210 +4392,210 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>464</v>
+        <v>470</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>465</v>
+        <v>471</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>466</v>
+        <v>472</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>467</v>
+        <v>473</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>468</v>
+        <v>474</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>470</v>
+        <v>476</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>471</v>
+        <v>477</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>472</v>
+        <v>478</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>474</v>
+        <v>480</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>475</v>
+        <v>481</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>476</v>
+        <v>482</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>477</v>
+        <v>483</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>478</v>
+        <v>484</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>479</v>
+        <v>485</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>480</v>
+        <v>486</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>481</v>
+        <v>487</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>482</v>
+        <v>488</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>483</v>
+        <v>489</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>485</v>
+        <v>491</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>486</v>
+        <v>492</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>487</v>
+        <v>493</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>488</v>
+        <v>494</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>489</v>
+        <v>495</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>490</v>
+        <v>496</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>492</v>
+        <v>498</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>493</v>
+        <v>499</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>494</v>
+        <v>500</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>495</v>
+        <v>501</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>496</v>
+        <v>502</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>497</v>
+        <v>503</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>498</v>
+        <v>504</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>499</v>
+        <v>505</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>500</v>
+        <v>506</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>501</v>
+        <v>507</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>502</v>
+        <v>508</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>503</v>
+        <v>509</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>504</v>
+        <v>510</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>505</v>
+        <v>511</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>506</v>
+        <v>512</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>507</v>
+        <v>513</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>508</v>
+        <v>514</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>509</v>
+        <v>515</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>510</v>
+        <v>516</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>234</v>
+        <v>240</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>511</v>
+        <v>517</v>
       </c>
     </row>
   </sheetData>

--- a/ig/DM-JUILLET-2026/ValueSet-JDV-J107-EnsembleSavoirFaire-RASS.xlsx
+++ b/ig/DM-JUILLET-2026/ValueSet-JDV-J107-EnsembleSavoirFaire-RASS.xlsx
@@ -154,7 +154,7 @@
     <t>SI08</t>
   </si>
   <si>
-    <t>Exercice infirmier en pratique avancée puériculture (SI)</t>
+    <t>Infirmier(ère) puériculteur(trice)</t>
   </si>
   <si>
     <t>SCD01</t>
